--- a/results/labN/model_results_labN.xlsx
+++ b/results/labN/model_results_labN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,127 +611,127 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>NDVI_only</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>DummyRegressor_mean</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.05839770282090817</v>
+        <v>-0.1391728230515243</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6606485359866821</v>
+        <v>0.6853948556216822</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5223140980964728</v>
+        <v>0.5410194805194807</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3998610859825829</v>
+        <v>0.4249350649350647</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.155704451122755</v>
+        <v>-0.116902391925716</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1352669545672854</v>
+        <v>0.06175766104691119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>GNDVI_only</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>DummyRegressor_mean</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.05976347404699234</v>
+        <v>-0.1391728230515243</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6610746536279091</v>
+        <v>0.6853948556216822</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5226151830908508</v>
+        <v>0.5410194805194807</v>
       </c>
       <c r="F8" t="n">
-        <v>0.400300032873198</v>
+        <v>0.4249350649350647</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1569458811488503</v>
+        <v>-0.116902391925716</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1360564801277424</v>
+        <v>0.06175766104691119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>NDRE_only</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>DummyRegressor_mean</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.05861277126344278</v>
+        <v>-0.1391728230515243</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6607156551017763</v>
+        <v>0.6853948556216822</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5223615352226965</v>
+        <v>0.5410194805194807</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3999302437933154</v>
+        <v>0.4249350649350647</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1571008314841487</v>
+        <v>-0.116902391925716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.136564253537771</v>
+        <v>0.06175766104691119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>RECI_only</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>DummyRegressor_mean</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.05738560676292415</v>
+        <v>-0.1391728230515243</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6603325868397373</v>
+        <v>0.6853948556216822</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5220907359027518</v>
+        <v>0.5410194805194807</v>
       </c>
       <c r="F10" t="n">
-        <v>0.399535449892291</v>
+        <v>0.4249350649350647</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1573905608504758</v>
+        <v>-0.116902391925716</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1372269824633975</v>
+        <v>0.06175766104691119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>RECI_only</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -740,238 +740,238 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1275857046605662</v>
+        <v>-0.1729919113258152</v>
       </c>
       <c r="D11" t="n">
-        <v>0.599801322887025</v>
+        <v>0.6954942459754827</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4527165700072008</v>
+        <v>0.5173895692177448</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3482524874367214</v>
+        <v>0.3886880162941568</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1710621068174498</v>
+        <v>-0.1468811132558628</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4140388376941432</v>
+        <v>0.1933837186150314</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>RECI_only</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.0152008660696612</v>
+        <v>-0.1734120485108015</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6470264317207297</v>
+        <v>0.6956187893894397</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4774993954721404</v>
+        <v>0.5172915085248735</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2307713026474112</v>
+        <v>0.3884916186313778</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1826087937569423</v>
+        <v>-0.1476188923001529</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2937758909698118</v>
+        <v>0.1943199009607361</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>RECI_only</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1181268517208296</v>
+        <v>-0.1737974019305837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.603044126953688</v>
+        <v>0.695733002071753</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4540915739589847</v>
+        <v>0.5172020422800703</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3420786014785151</v>
+        <v>0.3883124340788069</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1843742516492235</v>
+        <v>-0.1477512132991955</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4187301659827545</v>
+        <v>0.1950514659226023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>RECI_only</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>LinearRegression</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1149093513764388</v>
+        <v>-0.1742859331217923</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6041432238745038</v>
+        <v>0.6958777680739743</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4546200717852823</v>
+        <v>0.517089265090534</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3385758979184526</v>
+        <v>0.3880865619603149</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.186432770529808</v>
+        <v>-0.1479702887332127</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4163491788153854</v>
+        <v>0.1959875258116307</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>GNDVI_only</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1090015735701123</v>
+        <v>-0.0956839822400406</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6061561295156705</v>
+        <v>0.6721848021602699</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4556224736326131</v>
+        <v>0.5073335582353172</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3335677631210019</v>
+        <v>0.3601977202586464</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1920106382587233</v>
+        <v>-0.1554652042966337</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4145451863827591</v>
+        <v>0.2829976020852162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>N_test_only</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.2441782043728014</v>
+        <v>-0.05839770282090817</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7162874255378793</v>
+        <v>0.6606485359866821</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5832304034563955</v>
+        <v>0.5223140980964728</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4218624587944257</v>
+        <v>0.3998610859825829</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1940924014725512</v>
+        <v>-0.155704451122755</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2847949798122749</v>
+        <v>0.1352669545672854</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>GNDVI_only</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.02574077745222159</v>
+        <v>-0.09564582520053388</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6503765037781312</v>
+        <v>0.6721730976880984</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5236433333333319</v>
+        <v>0.5071741948781958</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3812666666666691</v>
+        <v>0.3598384391360028</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.202768471411318</v>
+        <v>-0.1567298138682463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.576760724070488</v>
+        <v>0.2855605180583696</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>GNDVI_only</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.1516754401889149</v>
+        <v>-0.09561838782888388</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6891457550685803</v>
+        <v>0.6721646812919726</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5164272795338866</v>
+        <v>0.5070551546367261</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3616401789444412</v>
+        <v>0.3595700655753076</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2286265229940816</v>
+        <v>-0.1569334436712616</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2622751865401684</v>
+        <v>0.2864626504383441</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>N_test_only</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.1564240372388732</v>
+        <v>-0.05976347404699234</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6905650391167881</v>
+        <v>0.6610746536279091</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5173220992930343</v>
+        <v>0.5226151830908508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3603983812695291</v>
+        <v>0.400300032873198</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2431353167304403</v>
+        <v>-0.1569458811488503</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2696852498443055</v>
+        <v>0.1360564801277424</v>
       </c>
     </row>
     <row r="20">
@@ -1006,92 +1006,92 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.1220978006049109</v>
+        <v>-0.05861277126344278</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6802387816054007</v>
+        <v>0.6607156551017763</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.5223615352226965</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4429999999999998</v>
+        <v>0.3999302437933154</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2484422034109522</v>
+        <v>-0.1571008314841487</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4049063799422755</v>
+        <v>0.136564253537771</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>NDRE_only</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.1650637938277129</v>
+        <v>-0.1279494372236811</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6931398781730529</v>
+        <v>0.6820101664841635</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5187539070020473</v>
+        <v>0.511502818473106</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3606528272915153</v>
+        <v>0.3822278984362335</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2501607110147878</v>
+        <v>-0.1571117932154932</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2727703405104128</v>
+        <v>0.2475823251184625</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>GNDVI_only</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>LinearRegression</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.2492307058082484</v>
+        <v>-0.09558456942828353</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7177403430210678</v>
+        <v>0.6721543073743157</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5539999999999999</v>
+        <v>0.5069026565628799</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3749999999999996</v>
+        <v>0.3592262620801874</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2619050003672038</v>
+        <v>-0.1572808508790235</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4983079259768049</v>
+        <v>0.2877362019644943</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>N_test_only</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1100,262 +1100,1462 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.1766473492419891</v>
+        <v>-0.05738560676292415</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6965771001704176</v>
+        <v>0.6603325868397373</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5206375042137802</v>
+        <v>0.5220907359027518</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3609819655297564</v>
+        <v>0.399535449892291</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2627603729495145</v>
+        <v>-0.1573905608504758</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2778147429010018</v>
+        <v>0.1372269824633975</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>NDRE_only</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.4976377675888255</v>
+        <v>-0.1280633129595172</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7858676733394752</v>
+        <v>0.6820445928719417</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6156</v>
+        <v>0.5113979701055118</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4750000000000001</v>
+        <v>0.3820267228225469</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3889548285442539</v>
+        <v>-0.1580830310269288</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5376362001078837</v>
+        <v>0.2492844545651767</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>NDRE_only</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.5280308613571512</v>
+        <v>-0.1281866134632754</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7938018294539513</v>
+        <v>0.6820818665528829</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6206433333333313</v>
+        <v>0.5112856594139306</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3832666666666709</v>
+        <v>0.3818112290306945</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4364970916564502</v>
+        <v>-0.1582442426159985</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3369832420407544</v>
+        <v>0.2501598837989663</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>NDRE_only</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MLPRegressor</t>
+          <t>LinearRegression</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.09379308488771199</v>
+        <v>-0.1283422597069288</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6716045338830725</v>
+        <v>0.6821289154266076</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5378893806399939</v>
+        <v>0.5111456278882567</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4135970897318735</v>
+        <v>0.3815425464678728</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4575468399116788</v>
+        <v>-0.1585169201428181</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3570738188174929</v>
+        <v>0.251329065260181</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>NDVI_only</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GradientBoostingRegressor</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.08655614070519957</v>
+        <v>0.01804832274490342</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6693790532159425</v>
+        <v>0.6363427358115681</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5445992009510391</v>
+        <v>0.4678946388253035</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4935223176582755</v>
+        <v>0.2533698885531352</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4831798832887535</v>
+        <v>-0.1666248061605207</v>
       </c>
       <c r="H27" t="n">
-        <v>0.837777803202008</v>
+        <v>0.3223192331508568</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>NDVI_only</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.1514156860870497</v>
+        <v>-0.0730524370005452</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6890680341564435</v>
+        <v>0.6652065321725206</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5329484338624322</v>
+        <v>0.5073039850182527</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5990440079364987</v>
+        <v>0.3834618563231524</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4912877679616311</v>
+        <v>-0.168232320433463</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5463933436285138</v>
+        <v>0.2735419416490295</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>multispectral_only</t>
+          <t>NDVI_only</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GradientBoostingRegressor</t>
+          <t>Lasso</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.5145282413314241</v>
+        <v>-0.07289375556723332</v>
       </c>
       <c r="D29" t="n">
-        <v>0.790286786481329</v>
+        <v>0.6651573454669195</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6259929562297564</v>
+        <v>0.5071774851662844</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4176619840455531</v>
+        <v>0.3832655370375904</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.6977031086193191</v>
+        <v>-0.1695954909027052</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3598862955927088</v>
+        <v>0.2760280162763279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>N_test_only</t>
+          <t>NDVI_only</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GradientBoostingRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2347939891914852</v>
+        <v>-0.07272437282159538</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7135810133364967</v>
+        <v>0.665104837646827</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5724111202892509</v>
+        <v>0.5070418278017785</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5378567076952012</v>
+        <v>0.383055005906789</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8087389923603912</v>
+        <v>-0.1698221287566031</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7323787248043633</v>
+        <v>0.276936335209542</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>NDVI_only</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.07251433684152997</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.665039721765882</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5068726992780613</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3827925297818948</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.1702050326926902</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2782107198349775</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1275857046605662</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.599801322887025</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.4527165700072008</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3482524874367214</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.1710621068174498</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4140388376941432</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.0152008660696612</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.6470264317207297</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.4774993954721404</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.2307713026474112</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.1826087937569423</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2937758909698118</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1181268517208296</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.603044126953688</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4540915739589847</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3420786014785151</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.1843742516492235</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4187301659827545</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1149093513764388</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6041432238745038</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.4546200717852823</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3385758979184526</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.186432770529808</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4163491788153854</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GNDVI_only</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.001451551217184877</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6426300125813443</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.4816919120497771</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3395705695243216</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.1899050043978302</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3459535378741556</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1090015735701123</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.6061561295156705</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.4556224736326131</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.3335677631210019</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.1920106382587233</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4145451863827591</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.2441782043728014</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.7162874255378793</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5832304034563955</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.4218624587944257</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.1940924014725512</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2847949798122749</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.02574077745222159</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.6503765037781312</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5236433333333319</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.3812666666666691</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.202768471411318</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.576760724070488</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RECI_only</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.1083947107819005</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6760724752273299</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5160400597788624</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.3645955395895835</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.2032166015297196</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3160342726000763</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NDRE_only</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SVR</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.05593525477796035</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6598795622727285</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5065022939400781</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.3496979421670134</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.2274636627483666</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3283635699689812</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.1516754401889149</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.6891457550685803</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5164272795338866</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.3616401789444412</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.2286265229940816</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2622751865401684</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.1564240372388732</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6905650391167881</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5173220992930343</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.3603983812695291</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.2431353167304403</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2696852498443055</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>N_test_only</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KNeighborsRegressor</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.1220978006049109</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.6802387816054007</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5398000000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.4429999999999998</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.2484422034109522</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.4049063799422755</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.1650637938277129</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6931398781730529</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5187539070020473</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.3606528272915153</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.2501607110147878</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2727703405104128</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KNeighborsRegressor</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.2492307058082484</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.7177403430210678</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5539999999999999</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.3749999999999996</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.2619050003672038</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.4983079259768049</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.1766473492419891</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6965771001704176</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5206375042137802</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.3609819655297564</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.2627603729495145</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2778147429010018</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NDRE_only</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KNeighborsRegressor</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.3458622284705843</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.7449829528250966</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5718000000000002</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.3140000000000003</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.2666892855608851</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.3607678605110407</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>RECI_only</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>KNeighborsRegressor</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.3651383844427913</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.7502990070631841</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.5795000000000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.4429999999999998</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.3445224962404141</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2681317933960735</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NDVI_only</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>MLPRegressor</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C50" t="n">
+        <v>-0.003582986103689567</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6433135184330907</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5316084169590619</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6014269116009463</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.3481505992309698</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.4287627270144758</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GNDVI_only</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>KNeighborsRegressor</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.381358097216185</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.7547431351128674</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.5962</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.5120000000000002</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.3609229347115337</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2945584809839602</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>GNDVI_only</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MLPRegressor</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.001470301048832834</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.642636028423117</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5314809200398745</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6001235337357029</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.3654346379976149</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4135689194250261</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NDVI_only</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KNeighborsRegressor</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.3144311090822125</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.7362324361232668</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.5883</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.5070000000000001</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.367361832532794</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.3923068649148773</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KNeighborsRegressor</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.4976377675888255</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.7858676733394752</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.4750000000000001</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.3889548285442539</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.5376362001078837</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NDRE_only</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.4287975903255623</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.7675936744861217</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.569526666666665</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.3385500000000037</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-0.3932526487133994</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3589619654238178</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.5280308613571512</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.7938018294539513</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.6206433333333313</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.3832666666666709</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.4364970916564502</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3369832420407544</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NDRE_only</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.2821283161392651</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.7271295234247133</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5515196196018578</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.440438082497268</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.4423125922012217</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.3386127866939443</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MLPRegressor</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.09379308488771199</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.6716045338830725</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5378893806399939</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.4135970897318735</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0.4575468399116788</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.3570738188174929</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.08655614070519957</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.6693790532159425</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5445992009510391</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.4935223176582755</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-0.4831798832887535</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.837777803202008</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>N_test_only</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.1514156860870497</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.6890680341564435</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5329484338624322</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.5990440079364987</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.4912877679616311</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.5463933436285138</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RECI_only</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.6755605539755973</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.831239354551713</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.673799999999998</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.6373333333333289</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.5181264723964608</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.3130480058921066</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RECI_only</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.5660945421726804</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.8036279271558596</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.6467752506944292</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.6244555457040777</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-0.6520190738187326</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.348817320227265</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>multispectral_only</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.5145282413314241</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.790286786481329</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.6259929562297564</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.4176619840455531</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-0.6977031086193191</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.3598862955927088</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NDVI_only</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.6960303278618469</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.8363014303733118</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6670733333333346</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.5023166666666612</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.7098585975133257</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.243720005483055</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>N_test_only</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.2347939891914852</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.7135810133364967</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5724111202892509</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.5378567076952012</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-0.8087389923603912</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.7323787248043633</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RECI_only</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MLPRegressor</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.0482061820168711</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.6574600841554274</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.5354138547354941</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-0.8494936414102439</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.086652021104657</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NDRE_only</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MLPRegressor</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.02512507228849126</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.6501812788782053</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5345974071642351</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.5997124045483941</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-0.8748677443722803</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.947605006311433</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>GNDVI_only</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.4920613425315548</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.7844032273716843</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.6095233333333369</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.4675499999999899</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-0.8884668929828191</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.6879750618861078</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>NDVI_only</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.7217605845407224</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.8426212616649513</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6695015362457233</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.5099436275727836</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-0.8974660489722404</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.3572449482859327</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MLPRegressor</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
         <v>-0.6241123067520788</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D70" t="n">
         <v>0.8183782172497089</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E70" t="n">
         <v>0.5977801122498602</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F70" t="n">
         <v>0.4481005197361738</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G70" t="n">
         <v>-0.9832812796118973</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H70" t="n">
         <v>0.9838197314818189</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GNDVI_only</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.6032444501925678</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.813103639972819</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.6358546889890159</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.5113150611524653</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-1.04185546824308</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.7809670579420949</v>
       </c>
     </row>
   </sheetData>
